--- a/010_input/00_Master_Input_Template.xlsx
+++ b/010_input/00_Master_Input_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/010_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{54E05085-9CEB-4B64-8994-AF27C5B8D64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9B79F5D-5947-4905-BF1E-A35CCBB61AFB}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{54E05085-9CEB-4B64-8994-AF27C5B8D64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAAD2880-5B32-443F-946F-F9F11A128EA4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57495" yWindow="-3300" windowWidth="14610" windowHeight="15585" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="kwh_kw_ratio" sheetId="1" r:id="rId1"/>
@@ -2279,6 +2279,7 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="2" max="2" width="15.140625" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
